--- a/data/courses.xlsx
+++ b/data/courses.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\20260915_chat-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4FFC79-6B29-42B0-B898-F2E1024E4A28}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788CEFED-C960-49F9-8823-BF0F53C9A7C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11062" uniqueCount="3273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11152" uniqueCount="3297">
   <si>
     <t>현대소설론세미나</t>
   </si>
@@ -9926,6 +9926,97 @@
   </si>
   <si>
     <t>정보보안전공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정신건강 사회복지 MD</t>
+  </si>
+  <si>
+    <t>커뮤니티 케어 MD</t>
+  </si>
+  <si>
+    <t>식생활안전관리 MD</t>
+  </si>
+  <si>
+    <t>스마트영양관리 MD</t>
+  </si>
+  <si>
+    <t>GX 융합디자이너 MD</t>
+  </si>
+  <si>
+    <t>정신건강사회복지론</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사례관리론</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중독과사회복지실천</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지역사회복지론</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사례관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장애인복지론</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노인복지론</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영양교육및상담</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식품위생학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공중보건학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단체급식관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식사요법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식생활관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영양판정및실험</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>외식산업의푸드테크와디자인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제품폼팩터디자인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공간폼팩터디자인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공공디자인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식품영양학전공</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10320,7 +10411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2411"/>
+  <dimension ref="A1:I2422"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.375" style="2" bestFit="1" customWidth="1"/>
@@ -10330,7 +10421,7 @@
     <col min="6" max="6" width="25.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.125" style="14" customWidth="1"/>
-    <col min="9" max="9" width="51.5" customWidth="1"/>
+    <col min="9" max="9" width="53.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -69716,74 +69807,473 @@
         <v>2111</v>
       </c>
     </row>
+    <row r="2216" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2216" s="9" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B2216" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2216" s="10"/>
+      <c r="D2216" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2216" s="11"/>
+      <c r="F2216" s="7" t="s">
+        <v>3278</v>
+      </c>
+      <c r="G2216" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2216" s="12" t="s">
+        <v>3257</v>
+      </c>
+      <c r="I2216" s="12" t="s">
+        <v>2485</v>
+      </c>
+    </row>
     <row r="2217" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H2217"/>
+      <c r="A2217" s="9" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B2217" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2217" s="10"/>
+      <c r="D2217" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2217" s="11"/>
+      <c r="F2217" s="7" t="s">
+        <v>3279</v>
+      </c>
+      <c r="G2217" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2217" s="12" t="s">
+        <v>3257</v>
+      </c>
+      <c r="I2217" s="12" t="s">
+        <v>2635</v>
+      </c>
     </row>
     <row r="2218" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H2218"/>
+      <c r="A2218" s="9" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B2218" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2218" s="10"/>
+      <c r="D2218" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2218" s="11"/>
+      <c r="F2218" s="7" t="s">
+        <v>3280</v>
+      </c>
+      <c r="G2218" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2218" s="12" t="s">
+        <v>3257</v>
+      </c>
+      <c r="I2218" s="12" t="s">
+        <v>2490</v>
+      </c>
     </row>
     <row r="2219" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H2219"/>
+      <c r="A2219" s="9" t="s">
+        <v>3274</v>
+      </c>
+      <c r="B2219" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2219" s="10"/>
+      <c r="D2219" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2219" s="11"/>
+      <c r="F2219" s="7" t="s">
+        <v>3281</v>
+      </c>
+      <c r="G2219" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2219" s="12" t="s">
+        <v>3257</v>
+      </c>
+      <c r="I2219" s="12" t="s">
+        <v>1721</v>
+      </c>
     </row>
     <row r="2220" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H2220"/>
+      <c r="A2220" s="9" t="s">
+        <v>3274</v>
+      </c>
+      <c r="B2220" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2220" s="10"/>
+      <c r="D2220" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2220" s="11"/>
+      <c r="F2220" s="7" t="s">
+        <v>3282</v>
+      </c>
+      <c r="G2220" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2220" s="12" t="s">
+        <v>3257</v>
+      </c>
+      <c r="I2220" s="12" t="s">
+        <v>2487</v>
+      </c>
     </row>
     <row r="2221" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H2221"/>
+      <c r="A2221" s="9" t="s">
+        <v>3274</v>
+      </c>
+      <c r="B2221" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2221" s="10"/>
+      <c r="D2221" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2221" s="11"/>
+      <c r="F2221" s="7" t="s">
+        <v>3283</v>
+      </c>
+      <c r="G2221" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2221" s="12" t="s">
+        <v>3257</v>
+      </c>
+      <c r="I2221" s="12" t="s">
+        <v>1709</v>
+      </c>
     </row>
     <row r="2222" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H2222"/>
+      <c r="A2222" s="9" t="s">
+        <v>3274</v>
+      </c>
+      <c r="B2222" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2222" s="10"/>
+      <c r="D2222" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2222" s="11"/>
+      <c r="F2222" s="7" t="s">
+        <v>3284</v>
+      </c>
+      <c r="G2222" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2222" s="12" t="s">
+        <v>3257</v>
+      </c>
+      <c r="I2222" s="12" t="s">
+        <v>2880</v>
+      </c>
     </row>
     <row r="2223" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H2223"/>
+      <c r="A2223" s="9" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B2223" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2223" s="10"/>
+      <c r="D2223" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2223" s="11"/>
+      <c r="F2223" s="7" t="s">
+        <v>3285</v>
+      </c>
+      <c r="G2223" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2223" s="12" t="s">
+        <v>3296</v>
+      </c>
+      <c r="I2223" s="12" t="s">
+        <v>1737</v>
+      </c>
     </row>
     <row r="2224" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H2224"/>
-    </row>
-    <row r="2225" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2225"/>
-    </row>
-    <row r="2226" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2226"/>
-    </row>
-    <row r="2227" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2227"/>
-    </row>
-    <row r="2228" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2228"/>
-    </row>
-    <row r="2255" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2255"/>
-    </row>
-    <row r="2256" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2256"/>
-    </row>
-    <row r="2257" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2257"/>
-    </row>
-    <row r="2258" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2258"/>
-    </row>
-    <row r="2259" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2259"/>
-    </row>
-    <row r="2260" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2260"/>
-    </row>
-    <row r="2261" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2261"/>
-    </row>
-    <row r="2262" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2262"/>
-    </row>
-    <row r="2263" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2263"/>
-    </row>
-    <row r="2264" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2264"/>
-    </row>
-    <row r="2265" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H2265"/>
+      <c r="A2224" s="9" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B2224" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2224" s="10"/>
+      <c r="D2224" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2224" s="11"/>
+      <c r="F2224" s="7" t="s">
+        <v>3286</v>
+      </c>
+      <c r="G2224" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2224" s="12" t="s">
+        <v>3296</v>
+      </c>
+      <c r="I2224" s="12" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2225" s="9" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B2225" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2225" s="10"/>
+      <c r="D2225" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2225" s="11"/>
+      <c r="F2225" s="7" t="s">
+        <v>3287</v>
+      </c>
+      <c r="G2225" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2225" s="12" t="s">
+        <v>3296</v>
+      </c>
+      <c r="I2225" s="12" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2226" s="9" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B2226" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2226" s="10"/>
+      <c r="D2226" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2226" s="11"/>
+      <c r="F2226" s="7" t="s">
+        <v>3288</v>
+      </c>
+      <c r="G2226" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2226" s="12" t="s">
+        <v>3296</v>
+      </c>
+      <c r="I2226" s="12" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2227" s="9" t="s">
+        <v>3276</v>
+      </c>
+      <c r="B2227" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2227" s="10"/>
+      <c r="D2227" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2227" s="11"/>
+      <c r="F2227" s="7" t="s">
+        <v>3289</v>
+      </c>
+      <c r="G2227" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2227" s="12" t="s">
+        <v>3296</v>
+      </c>
+      <c r="I2227" s="12" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2228" s="9" t="s">
+        <v>3276</v>
+      </c>
+      <c r="B2228" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2228" s="10"/>
+      <c r="D2228" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2228" s="11"/>
+      <c r="F2228" s="7" t="s">
+        <v>3290</v>
+      </c>
+      <c r="G2228" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2228" s="12" t="s">
+        <v>3296</v>
+      </c>
+      <c r="I2228" s="12" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2229" s="9" t="s">
+        <v>3276</v>
+      </c>
+      <c r="B2229" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2229" s="10"/>
+      <c r="D2229" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2229" s="11"/>
+      <c r="F2229" s="7" t="s">
+        <v>3291</v>
+      </c>
+      <c r="G2229" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2229" s="12" t="s">
+        <v>3296</v>
+      </c>
+      <c r="I2229" s="12" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2230" s="9" t="s">
+        <v>3276</v>
+      </c>
+      <c r="B2230" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2230" s="10"/>
+      <c r="D2230" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2230" s="11"/>
+      <c r="F2230" s="7" t="s">
+        <v>3292</v>
+      </c>
+      <c r="G2230" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2230" s="12" t="s">
+        <v>3258</v>
+      </c>
+      <c r="I2230" s="12" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2231" s="9" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B2231" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2231" s="10"/>
+      <c r="D2231" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2231" s="11"/>
+      <c r="F2231" s="7" t="s">
+        <v>3293</v>
+      </c>
+      <c r="G2231" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2231" s="12" t="s">
+        <v>3258</v>
+      </c>
+      <c r="I2231" s="12" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2232" s="9" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B2232" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2232" s="10"/>
+      <c r="D2232" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2232" s="11"/>
+      <c r="F2232" s="7" t="s">
+        <v>3294</v>
+      </c>
+      <c r="G2232" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2232" s="12" t="s">
+        <v>3258</v>
+      </c>
+      <c r="I2232" s="12" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2233" s="9" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B2233" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2233" s="10"/>
+      <c r="D2233" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2233" s="11"/>
+      <c r="F2233" s="7" t="s">
+        <v>3295</v>
+      </c>
+      <c r="G2233" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2233" s="12" t="s">
+        <v>3258</v>
+      </c>
+      <c r="I2233" s="12" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H2234"/>
+    </row>
+    <row r="2235" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H2235"/>
+    </row>
+    <row r="2236" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H2236"/>
+    </row>
+    <row r="2237" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H2237"/>
+    </row>
+    <row r="2238" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H2238"/>
+    </row>
+    <row r="2239" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H2239"/>
     </row>
     <row r="2266" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H2266"/>
@@ -70222,6 +70712,39 @@
     </row>
     <row r="2411" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H2411"/>
+    </row>
+    <row r="2412" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H2412"/>
+    </row>
+    <row r="2413" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H2413"/>
+    </row>
+    <row r="2414" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H2414"/>
+    </row>
+    <row r="2415" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H2415"/>
+    </row>
+    <row r="2416" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H2416"/>
+    </row>
+    <row r="2417" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H2417"/>
+    </row>
+    <row r="2418" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H2418"/>
+    </row>
+    <row r="2419" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H2419"/>
+    </row>
+    <row r="2420" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H2420"/>
+    </row>
+    <row r="2421" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H2421"/>
+    </row>
+    <row r="2422" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H2422"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/courses.xlsx
+++ b/data/courses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\20260915_chat-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4563FCE4-316C-45D2-B082-D319D08255A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E54C912-F423-4FDC-A428-CA302FE58F90}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9695,9 +9695,6 @@
     <t>지능형자율주행이동체공학</t>
   </si>
   <si>
-    <t>보석공예작품Ⅱ</t>
-  </si>
-  <si>
     <t>금속리빙오브제Ⅱ</t>
   </si>
   <si>
@@ -10036,6 +10033,10 @@
   </si>
   <si>
     <t>AI생물정보분석학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보석공예작품연구Ⅱ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -25472,7 +25473,7 @@
         <v>2774</v>
       </c>
       <c r="F557" s="3" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="G557" s="3">
         <v>3</v>
@@ -32219,7 +32220,7 @@
       </c>
       <c r="H807" s="12"/>
       <c r="I807" s="12" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="808" spans="1:9" x14ac:dyDescent="0.3">
@@ -34519,7 +34520,7 @@
     </row>
     <row r="893" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A893" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B893" s="5" t="s">
         <v>2773</v>
@@ -34546,7 +34547,7 @@
     </row>
     <row r="894" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A894" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B894" s="5" t="s">
         <v>2773</v>
@@ -34573,7 +34574,7 @@
     </row>
     <row r="895" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A895" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B895" s="5" t="s">
         <v>2773</v>
@@ -34600,7 +34601,7 @@
     </row>
     <row r="896" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A896" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B896" s="5" t="s">
         <v>2773</v>
@@ -34627,7 +34628,7 @@
     </row>
     <row r="897" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A897" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B897" s="5" t="s">
         <v>2773</v>
@@ -34654,7 +34655,7 @@
     </row>
     <row r="898" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A898" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B898" s="5" t="s">
         <v>2773</v>
@@ -34681,7 +34682,7 @@
     </row>
     <row r="899" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A899" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B899" s="5" t="s">
         <v>2773</v>
@@ -34708,7 +34709,7 @@
     </row>
     <row r="900" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A900" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B900" s="5" t="s">
         <v>2773</v>
@@ -34735,7 +34736,7 @@
     </row>
     <row r="901" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A901" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B901" s="5" t="s">
         <v>2773</v>
@@ -34762,7 +34763,7 @@
     </row>
     <row r="902" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A902" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B902" s="5" t="s">
         <v>2773</v>
@@ -34789,7 +34790,7 @@
     </row>
     <row r="903" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A903" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B903" s="5" t="s">
         <v>2773</v>
@@ -34816,7 +34817,7 @@
     </row>
     <row r="904" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A904" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B904" s="5" t="s">
         <v>2773</v>
@@ -34843,7 +34844,7 @@
     </row>
     <row r="905" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A905" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B905" s="5" t="s">
         <v>2773</v>
@@ -34870,7 +34871,7 @@
     </row>
     <row r="906" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A906" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B906" s="5" t="s">
         <v>2773</v>
@@ -34897,7 +34898,7 @@
     </row>
     <row r="907" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A907" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B907" s="5" t="s">
         <v>2773</v>
@@ -34924,7 +34925,7 @@
     </row>
     <row r="908" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A908" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B908" s="5" t="s">
         <v>2773</v>
@@ -34951,7 +34952,7 @@
     </row>
     <row r="909" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A909" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B909" s="5" t="s">
         <v>2773</v>
@@ -34978,7 +34979,7 @@
     </row>
     <row r="910" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A910" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B910" s="5" t="s">
         <v>2773</v>
@@ -35005,7 +35006,7 @@
     </row>
     <row r="911" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A911" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B911" s="5" t="s">
         <v>2773</v>
@@ -35032,7 +35033,7 @@
     </row>
     <row r="912" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A912" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B912" s="5" t="s">
         <v>2773</v>
@@ -35059,7 +35060,7 @@
     </row>
     <row r="913" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A913" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B913" s="5" t="s">
         <v>2773</v>
@@ -35086,7 +35087,7 @@
     </row>
     <row r="914" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A914" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B914" s="5" t="s">
         <v>2773</v>
@@ -35113,7 +35114,7 @@
     </row>
     <row r="915" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A915" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B915" s="5" t="s">
         <v>2773</v>
@@ -35140,7 +35141,7 @@
     </row>
     <row r="916" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A916" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B916" s="5" t="s">
         <v>2773</v>
@@ -35167,7 +35168,7 @@
     </row>
     <row r="917" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A917" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B917" s="5" t="s">
         <v>2773</v>
@@ -35194,7 +35195,7 @@
     </row>
     <row r="918" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A918" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B918" s="5" t="s">
         <v>2773</v>
@@ -35221,7 +35222,7 @@
     </row>
     <row r="919" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A919" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B919" s="5" t="s">
         <v>2773</v>
@@ -35248,7 +35249,7 @@
     </row>
     <row r="920" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A920" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B920" s="5" t="s">
         <v>2773</v>
@@ -35275,7 +35276,7 @@
     </row>
     <row r="921" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A921" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B921" s="5" t="s">
         <v>2773</v>
@@ -35302,7 +35303,7 @@
     </row>
     <row r="922" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A922" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B922" s="5" t="s">
         <v>2773</v>
@@ -35329,7 +35330,7 @@
     </row>
     <row r="923" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A923" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B923" s="5" t="s">
         <v>2773</v>
@@ -35356,7 +35357,7 @@
     </row>
     <row r="924" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A924" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B924" s="5" t="s">
         <v>2773</v>
@@ -35383,7 +35384,7 @@
     </row>
     <row r="925" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A925" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B925" s="5" t="s">
         <v>2773</v>
@@ -35410,7 +35411,7 @@
     </row>
     <row r="926" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A926" s="8" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B926" s="5" t="s">
         <v>2773</v>
@@ -51080,7 +51081,7 @@
       </c>
       <c r="H1506" s="12"/>
       <c r="I1506" s="12" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="1507" spans="1:9" x14ac:dyDescent="0.3">
@@ -64333,7 +64334,7 @@
       </c>
       <c r="H1997" s="12"/>
       <c r="I1997" s="12" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="1998" spans="1:9" x14ac:dyDescent="0.3">
@@ -64414,7 +64415,7 @@
       </c>
       <c r="H2000" s="12"/>
       <c r="I2000" s="12" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="2001" spans="1:9" x14ac:dyDescent="0.3">
@@ -64522,7 +64523,7 @@
       </c>
       <c r="H2004" s="12"/>
       <c r="I2004" s="12" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="2005" spans="1:9" x14ac:dyDescent="0.3">
@@ -64763,7 +64764,7 @@
       </c>
       <c r="H2013" s="12"/>
       <c r="I2013" s="12" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
     </row>
     <row r="2014" spans="1:9" x14ac:dyDescent="0.3">
@@ -64871,7 +64872,7 @@
       </c>
       <c r="H2017" s="12"/>
       <c r="I2017" s="12" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="2018" spans="1:9" x14ac:dyDescent="0.3">
@@ -64898,7 +64899,7 @@
       </c>
       <c r="H2018" s="12"/>
       <c r="I2018" s="12" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="2019" spans="1:9" x14ac:dyDescent="0.3">
@@ -65289,7 +65290,7 @@
       </c>
       <c r="E2034" s="11"/>
       <c r="F2034" s="7" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="G2034" s="7">
         <v>3</v>
@@ -65648,7 +65649,7 @@
         <v>1509</v>
       </c>
       <c r="I2048" s="12" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="2049" spans="1:9" x14ac:dyDescent="0.3">
@@ -65689,7 +65690,7 @@
       </c>
       <c r="E2050" s="11"/>
       <c r="F2050" s="7" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="G2050" s="7">
         <v>3</v>
@@ -65914,7 +65915,7 @@
       </c>
       <c r="E2059" s="11"/>
       <c r="F2059" s="7" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="G2059" s="7">
         <v>3</v>
@@ -66070,7 +66071,7 @@
         <v>3</v>
       </c>
       <c r="H2065" s="12" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="I2065" s="12" t="s">
         <v>2171</v>
@@ -66095,7 +66096,7 @@
         <v>3</v>
       </c>
       <c r="H2066" s="12" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="I2066" s="13" t="s">
         <v>1532</v>
@@ -67073,7 +67074,7 @@
         <v>1517</v>
       </c>
       <c r="I2105" s="12" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="2106" spans="1:9" x14ac:dyDescent="0.3">
@@ -67123,7 +67124,7 @@
         <v>1519</v>
       </c>
       <c r="I2107" s="12" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
     </row>
     <row r="2108" spans="1:9" x14ac:dyDescent="0.3">
@@ -67198,7 +67199,7 @@
         <v>616</v>
       </c>
       <c r="I2110" s="12" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="2111" spans="1:9" x14ac:dyDescent="0.3">
@@ -67239,7 +67240,7 @@
       </c>
       <c r="E2112" s="11"/>
       <c r="F2112" s="7" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="G2112" s="7">
         <v>3</v>
@@ -67248,7 +67249,7 @@
         <v>616</v>
       </c>
       <c r="I2112" s="12" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="2113" spans="1:9" x14ac:dyDescent="0.3">
@@ -67314,7 +67315,7 @@
       </c>
       <c r="E2115" s="11"/>
       <c r="F2115" s="7" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="G2115" s="7">
         <v>3</v>
@@ -67539,7 +67540,7 @@
       </c>
       <c r="E2124" s="11"/>
       <c r="F2124" s="7" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="G2124" s="7">
         <v>3</v>
@@ -67573,7 +67574,7 @@
         <v>775</v>
       </c>
       <c r="I2125" s="12" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="2126" spans="1:9" x14ac:dyDescent="0.3">
@@ -67595,7 +67596,7 @@
         <v>3</v>
       </c>
       <c r="H2126" s="12" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="I2126" s="12" t="s">
         <v>2265</v>
@@ -67620,7 +67621,7 @@
         <v>3</v>
       </c>
       <c r="H2127" s="12" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="I2127" s="12" t="s">
         <v>2268</v>
@@ -67773,7 +67774,7 @@
         <v>1518</v>
       </c>
       <c r="I2133" s="12" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="2134" spans="1:9" x14ac:dyDescent="0.3">
@@ -67795,7 +67796,7 @@
         <v>2</v>
       </c>
       <c r="H2134" s="12" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="I2134" s="12" t="s">
         <v>2435</v>
@@ -67820,7 +67821,7 @@
         <v>2</v>
       </c>
       <c r="H2135" s="12" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="I2135" s="12" t="s">
         <v>2439</v>
@@ -67845,7 +67846,7 @@
         <v>2</v>
       </c>
       <c r="H2136" s="12" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="I2136" s="12" t="s">
         <v>2440</v>
@@ -67870,7 +67871,7 @@
         <v>2</v>
       </c>
       <c r="H2137" s="12" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="I2137" s="12" t="s">
         <v>2442</v>
@@ -67895,7 +67896,7 @@
         <v>2</v>
       </c>
       <c r="H2138" s="12" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="I2138" s="12" t="s">
         <v>2447</v>
@@ -67920,7 +67921,7 @@
         <v>3</v>
       </c>
       <c r="H2139" s="12" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I2139" s="12" t="s">
         <v>2609</v>
@@ -67945,7 +67946,7 @@
         <v>3</v>
       </c>
       <c r="H2140" s="12" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I2140" s="12" t="s">
         <v>2138</v>
@@ -67970,7 +67971,7 @@
         <v>3</v>
       </c>
       <c r="H2141" s="12" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I2141" s="12" t="s">
         <v>2483</v>
@@ -67989,13 +67990,13 @@
       </c>
       <c r="E2142" s="11"/>
       <c r="F2142" s="7" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="G2142" s="7">
         <v>3</v>
       </c>
       <c r="H2142" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2142" s="12" t="s">
         <v>2409</v>
@@ -68020,7 +68021,7 @@
         <v>2</v>
       </c>
       <c r="H2143" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2143" s="12" t="s">
         <v>2411</v>
@@ -68039,13 +68040,13 @@
       </c>
       <c r="E2144" s="11"/>
       <c r="F2144" s="7" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="G2144" s="7">
         <v>2</v>
       </c>
       <c r="H2144" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2144" s="12" t="s">
         <v>3019</v>
@@ -68070,7 +68071,7 @@
         <v>2</v>
       </c>
       <c r="H2145" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2145" s="12" t="s">
         <v>2414</v>
@@ -68095,7 +68096,7 @@
         <v>3</v>
       </c>
       <c r="H2146" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2146" s="12" t="s">
         <v>2418</v>
@@ -68120,7 +68121,7 @@
         <v>3</v>
       </c>
       <c r="H2147" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2147" s="12" t="s">
         <v>2423</v>
@@ -68145,7 +68146,7 @@
         <v>3</v>
       </c>
       <c r="H2148" s="12" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I2148" s="12" t="s">
         <v>2507</v>
@@ -68170,7 +68171,7 @@
         <v>3</v>
       </c>
       <c r="H2149" s="12" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I2149" s="12" t="s">
         <v>2511</v>
@@ -68195,7 +68196,7 @@
         <v>3</v>
       </c>
       <c r="H2150" s="12" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I2150" s="12" t="s">
         <v>2767</v>
@@ -68220,7 +68221,7 @@
         <v>3</v>
       </c>
       <c r="H2151" s="12" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I2151" s="12" t="s">
         <v>2520</v>
@@ -68239,13 +68240,13 @@
       </c>
       <c r="E2152" s="11"/>
       <c r="F2152" s="7" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="G2152" s="7">
         <v>3</v>
       </c>
       <c r="H2152" s="12" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="I2152" s="12" t="s">
         <v>1599</v>
@@ -68270,7 +68271,7 @@
         <v>3</v>
       </c>
       <c r="H2153" s="12" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="I2153" s="12" t="s">
         <v>1610</v>
@@ -68295,7 +68296,7 @@
         <v>3</v>
       </c>
       <c r="H2154" s="12" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="I2154" s="12" t="s">
         <v>2839</v>
@@ -68320,7 +68321,7 @@
         <v>3</v>
       </c>
       <c r="H2155" s="12" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="I2155" s="12" t="s">
         <v>2844</v>
@@ -68345,7 +68346,7 @@
         <v>3</v>
       </c>
       <c r="H2156" s="12" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="I2156" s="12" t="s">
         <v>2147</v>
@@ -68370,7 +68371,7 @@
         <v>3</v>
       </c>
       <c r="H2157" s="12" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="I2157" s="12" t="s">
         <v>2148</v>
@@ -68395,7 +68396,7 @@
         <v>3</v>
       </c>
       <c r="H2158" s="12" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="I2158" s="12" t="s">
         <v>2164</v>
@@ -68420,10 +68421,10 @@
         <v>3</v>
       </c>
       <c r="H2159" s="12" t="s">
+        <v>3226</v>
+      </c>
+      <c r="I2159" s="12" t="s">
         <v>3227</v>
-      </c>
-      <c r="I2159" s="12" t="s">
-        <v>3228</v>
       </c>
     </row>
     <row r="2160" spans="1:9" x14ac:dyDescent="0.3">
@@ -68445,7 +68446,7 @@
         <v>3</v>
       </c>
       <c r="H2160" s="12" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="I2160" s="12" t="s">
         <v>2154</v>
@@ -68470,7 +68471,7 @@
         <v>3</v>
       </c>
       <c r="H2161" s="12" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="I2161" s="12" t="s">
         <v>2173</v>
@@ -68489,16 +68490,16 @@
       </c>
       <c r="E2162" s="11"/>
       <c r="F2162" s="7" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="G2162" s="7">
         <v>3</v>
       </c>
       <c r="H2162" s="12" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="I2162" s="12" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="2163" spans="1:9" x14ac:dyDescent="0.3">
@@ -68520,7 +68521,7 @@
         <v>3</v>
       </c>
       <c r="H2163" s="12" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="I2163" s="12" t="s">
         <v>1899</v>
@@ -68539,13 +68540,13 @@
       </c>
       <c r="E2164" s="11"/>
       <c r="F2164" s="7" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="G2164" s="7">
         <v>3</v>
       </c>
       <c r="H2164" s="12" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="I2164" s="12" t="s">
         <v>1902</v>
@@ -68570,7 +68571,7 @@
         <v>3</v>
       </c>
       <c r="H2165" s="12" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="I2165" s="12" t="s">
         <v>1896</v>
@@ -68595,7 +68596,7 @@
         <v>3</v>
       </c>
       <c r="H2166" s="12" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="I2166" s="12" t="s">
         <v>2810</v>
@@ -68620,7 +68621,7 @@
         <v>3</v>
       </c>
       <c r="H2167" s="12" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="I2167" s="12" t="s">
         <v>2563</v>
@@ -68645,7 +68646,7 @@
         <v>3</v>
       </c>
       <c r="H2168" s="12" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="I2168" s="12" t="s">
         <v>3128</v>
@@ -68670,10 +68671,10 @@
         <v>3</v>
       </c>
       <c r="H2169" s="12" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="I2169" s="12" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="2170" spans="1:9" x14ac:dyDescent="0.3">
@@ -68695,10 +68696,10 @@
         <v>2</v>
       </c>
       <c r="H2170" s="12" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="I2170" s="12" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="2171" spans="1:9" x14ac:dyDescent="0.3">
@@ -68720,10 +68721,10 @@
         <v>3</v>
       </c>
       <c r="H2171" s="12" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="I2171" s="12" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="2172" spans="1:9" x14ac:dyDescent="0.3">
@@ -68745,10 +68746,10 @@
         <v>3</v>
       </c>
       <c r="H2172" s="12" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="I2172" s="12" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="2173" spans="1:9" x14ac:dyDescent="0.3">
@@ -68770,7 +68771,7 @@
         <v>3</v>
       </c>
       <c r="H2173" s="12" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="I2173" s="12" t="s">
         <v>2543</v>
@@ -68795,7 +68796,7 @@
         <v>3</v>
       </c>
       <c r="H2174" s="12" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="I2174" s="12" t="s">
         <v>2543</v>
@@ -68820,7 +68821,7 @@
         <v>3</v>
       </c>
       <c r="H2175" s="12" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="I2175" s="12" t="s">
         <v>2543</v>
@@ -68845,7 +68846,7 @@
         <v>3</v>
       </c>
       <c r="H2176" s="12" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I2176" s="12" t="s">
         <v>1704</v>
@@ -68870,7 +68871,7 @@
         <v>3</v>
       </c>
       <c r="H2177" s="12" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I2177" s="12" t="s">
         <v>1718</v>
@@ -68895,7 +68896,7 @@
         <v>3</v>
       </c>
       <c r="H2178" s="12" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I2178" s="12" t="s">
         <v>1712</v>
@@ -68920,7 +68921,7 @@
         <v>3</v>
       </c>
       <c r="H2179" s="12" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I2179" s="12" t="s">
         <v>2877</v>
@@ -68945,7 +68946,7 @@
         <v>3</v>
       </c>
       <c r="H2180" s="12" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I2180" s="12" t="s">
         <v>2879</v>
@@ -68970,7 +68971,7 @@
         <v>3</v>
       </c>
       <c r="H2181" s="12" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I2181" s="12" t="s">
         <v>1728</v>
@@ -68995,7 +68996,7 @@
         <v>3</v>
       </c>
       <c r="H2182" s="12" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I2182" s="12" t="s">
         <v>1708</v>
@@ -69020,7 +69021,7 @@
         <v>3</v>
       </c>
       <c r="H2183" s="12" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I2183" s="12" t="s">
         <v>2888</v>
@@ -69045,7 +69046,7 @@
         <v>3</v>
       </c>
       <c r="H2184" s="12" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="I2184" s="12" t="s">
         <v>2238</v>
@@ -69070,7 +69071,7 @@
         <v>3</v>
       </c>
       <c r="H2185" s="12" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="I2185" s="12" t="s">
         <v>2247</v>
@@ -69095,10 +69096,10 @@
         <v>3</v>
       </c>
       <c r="H2186" s="12" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="I2186" s="12" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="2187" spans="1:9" x14ac:dyDescent="0.3">
@@ -69120,7 +69121,7 @@
         <v>3</v>
       </c>
       <c r="H2187" s="12" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I2187" s="12" t="s">
         <v>2620</v>
@@ -69145,7 +69146,7 @@
         <v>3</v>
       </c>
       <c r="H2188" s="12" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I2188" s="12" t="s">
         <v>2625</v>
@@ -69170,7 +69171,7 @@
         <v>3</v>
       </c>
       <c r="H2189" s="12" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I2189" s="12" t="s">
         <v>2628</v>
@@ -69195,7 +69196,7 @@
         <v>3</v>
       </c>
       <c r="H2190" s="12" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="I2190" s="12" t="s">
         <v>1544</v>
@@ -69220,7 +69221,7 @@
         <v>3</v>
       </c>
       <c r="H2191" s="12" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="I2191" s="12" t="s">
         <v>2212</v>
@@ -69245,7 +69246,7 @@
         <v>3</v>
       </c>
       <c r="H2192" s="12" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="I2192" s="12" t="s">
         <v>2225</v>
@@ -69370,7 +69371,7 @@
         <v>3</v>
       </c>
       <c r="H2197" s="12" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I2197" s="12" t="s">
         <v>2568</v>
@@ -69395,7 +69396,7 @@
         <v>3</v>
       </c>
       <c r="H2198" s="12" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I2198" s="12" t="s">
         <v>2569</v>
@@ -69420,7 +69421,7 @@
         <v>3</v>
       </c>
       <c r="H2199" s="12" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I2199" s="12" t="s">
         <v>2571</v>
@@ -69445,7 +69446,7 @@
         <v>3</v>
       </c>
       <c r="H2200" s="12" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I2200" s="12" t="s">
         <v>2575</v>
@@ -69470,7 +69471,7 @@
         <v>3</v>
       </c>
       <c r="H2201" s="12" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="I2201" s="12" t="s">
         <v>1831</v>
@@ -69495,7 +69496,7 @@
         <v>3</v>
       </c>
       <c r="H2202" s="12" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="I2202" s="12" t="s">
         <v>1829</v>
@@ -69520,7 +69521,7 @@
         <v>3</v>
       </c>
       <c r="H2203" s="12" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="I2203" s="12" t="s">
         <v>1846</v>
@@ -69545,7 +69546,7 @@
         <v>3</v>
       </c>
       <c r="H2204" s="12" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="I2204" s="12" t="s">
         <v>1854</v>
@@ -69564,16 +69565,16 @@
       </c>
       <c r="E2205" s="11"/>
       <c r="F2205" s="7" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="G2205" s="7">
         <v>3</v>
       </c>
       <c r="H2205" s="12" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="I2205" s="12" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="2206" spans="1:9" x14ac:dyDescent="0.3">
@@ -69589,16 +69590,16 @@
       </c>
       <c r="E2206" s="11"/>
       <c r="F2206" s="7" t="s">
-        <v>3213</v>
+        <v>3300</v>
       </c>
       <c r="G2206" s="7">
         <v>3</v>
       </c>
       <c r="H2206" s="12" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="I2206" s="12" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="2207" spans="1:9" x14ac:dyDescent="0.3">
@@ -69614,16 +69615,16 @@
       </c>
       <c r="E2207" s="11"/>
       <c r="F2207" s="7" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="G2207" s="7">
         <v>3</v>
       </c>
       <c r="H2207" s="12" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="I2207" s="12" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="2208" spans="1:9" x14ac:dyDescent="0.3">
@@ -69639,16 +69640,16 @@
       </c>
       <c r="E2208" s="11"/>
       <c r="F2208" s="7" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="G2208" s="7">
         <v>3</v>
       </c>
       <c r="H2208" s="12" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="I2208" s="12" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="2209" spans="1:9" x14ac:dyDescent="0.3">
@@ -69670,7 +69671,7 @@
         <v>3</v>
       </c>
       <c r="H2209" s="12" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="I2209" s="12" t="s">
         <v>2268</v>
@@ -69689,16 +69690,16 @@
       </c>
       <c r="E2210" s="11"/>
       <c r="F2210" s="7" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="G2210" s="7">
         <v>3</v>
       </c>
       <c r="H2210" s="12" t="s">
+        <v>3238</v>
+      </c>
+      <c r="I2210" s="12" t="s">
         <v>3239</v>
-      </c>
-      <c r="I2210" s="12" t="s">
-        <v>3240</v>
       </c>
     </row>
     <row r="2211" spans="1:9" x14ac:dyDescent="0.3">
@@ -69720,7 +69721,7 @@
         <v>3</v>
       </c>
       <c r="H2211" s="12" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="I2211" s="12" t="s">
         <v>2996</v>
@@ -69745,7 +69746,7 @@
         <v>3</v>
       </c>
       <c r="H2212" s="12" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="I2212" s="12" t="s">
         <v>2071</v>
@@ -69770,7 +69771,7 @@
         <v>3</v>
       </c>
       <c r="H2213" s="12" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="I2213" s="12" t="s">
         <v>2105</v>
@@ -69795,7 +69796,7 @@
         <v>3</v>
       </c>
       <c r="H2214" s="12" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="I2214" s="12" t="s">
         <v>2101</v>
@@ -69820,7 +69821,7 @@
         <v>3</v>
       </c>
       <c r="H2215" s="12" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="I2215" s="12" t="s">
         <v>2110</v>
@@ -69828,7 +69829,7 @@
     </row>
     <row r="2216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2216" s="9" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="B2216" s="5" t="s">
         <v>2768</v>
@@ -69839,13 +69840,13 @@
       </c>
       <c r="E2216" s="11"/>
       <c r="F2216" s="7" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="G2216" s="7">
         <v>3</v>
       </c>
       <c r="H2216" s="12" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I2216" s="12" t="s">
         <v>2484</v>
@@ -69853,7 +69854,7 @@
     </row>
     <row r="2217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2217" s="9" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="B2217" s="5" t="s">
         <v>2768</v>
@@ -69864,13 +69865,13 @@
       </c>
       <c r="E2217" s="11"/>
       <c r="F2217" s="7" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="G2217" s="7">
         <v>3</v>
       </c>
       <c r="H2217" s="12" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I2217" s="12" t="s">
         <v>2634</v>
@@ -69878,7 +69879,7 @@
     </row>
     <row r="2218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2218" s="9" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="B2218" s="5" t="s">
         <v>2768</v>
@@ -69889,13 +69890,13 @@
       </c>
       <c r="E2218" s="11"/>
       <c r="F2218" s="7" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="G2218" s="7">
         <v>3</v>
       </c>
       <c r="H2218" s="12" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I2218" s="12" t="s">
         <v>2489</v>
@@ -69903,7 +69904,7 @@
     </row>
     <row r="2219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2219" s="9" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="B2219" s="5" t="s">
         <v>2768</v>
@@ -69914,13 +69915,13 @@
       </c>
       <c r="E2219" s="11"/>
       <c r="F2219" s="7" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="G2219" s="7">
         <v>3</v>
       </c>
       <c r="H2219" s="12" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I2219" s="12" t="s">
         <v>1720</v>
@@ -69928,7 +69929,7 @@
     </row>
     <row r="2220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2220" s="9" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="B2220" s="5" t="s">
         <v>2768</v>
@@ -69939,13 +69940,13 @@
       </c>
       <c r="E2220" s="11"/>
       <c r="F2220" s="7" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="G2220" s="7">
         <v>3</v>
       </c>
       <c r="H2220" s="12" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I2220" s="12" t="s">
         <v>2486</v>
@@ -69953,7 +69954,7 @@
     </row>
     <row r="2221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2221" s="9" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="B2221" s="5" t="s">
         <v>2768</v>
@@ -69964,13 +69965,13 @@
       </c>
       <c r="E2221" s="11"/>
       <c r="F2221" s="7" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="G2221" s="7">
         <v>3</v>
       </c>
       <c r="H2221" s="12" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I2221" s="12" t="s">
         <v>1708</v>
@@ -69978,7 +69979,7 @@
     </row>
     <row r="2222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2222" s="9" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="B2222" s="5" t="s">
         <v>2768</v>
@@ -69989,13 +69990,13 @@
       </c>
       <c r="E2222" s="11"/>
       <c r="F2222" s="7" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="G2222" s="7">
         <v>3</v>
       </c>
       <c r="H2222" s="12" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I2222" s="12" t="s">
         <v>2879</v>
@@ -70003,7 +70004,7 @@
     </row>
     <row r="2223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2223" s="9" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="B2223" s="5" t="s">
         <v>2768</v>
@@ -70014,13 +70015,13 @@
       </c>
       <c r="E2223" s="11"/>
       <c r="F2223" s="7" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="G2223" s="7">
         <v>3</v>
       </c>
       <c r="H2223" s="12" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="I2223" s="12" t="s">
         <v>1736</v>
@@ -70028,7 +70029,7 @@
     </row>
     <row r="2224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2224" s="9" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="B2224" s="5" t="s">
         <v>2768</v>
@@ -70039,13 +70040,13 @@
       </c>
       <c r="E2224" s="11"/>
       <c r="F2224" s="7" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="G2224" s="7">
         <v>3</v>
       </c>
       <c r="H2224" s="12" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="I2224" s="12" t="s">
         <v>1750</v>
@@ -70053,7 +70054,7 @@
     </row>
     <row r="2225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2225" s="9" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="B2225" s="5" t="s">
         <v>2768</v>
@@ -70064,13 +70065,13 @@
       </c>
       <c r="E2225" s="11"/>
       <c r="F2225" s="7" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="G2225" s="7">
         <v>3</v>
       </c>
       <c r="H2225" s="12" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="I2225" s="12" t="s">
         <v>1742</v>
@@ -70078,7 +70079,7 @@
     </row>
     <row r="2226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2226" s="9" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="B2226" s="5" t="s">
         <v>2768</v>
@@ -70089,13 +70090,13 @@
       </c>
       <c r="E2226" s="11"/>
       <c r="F2226" s="7" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="G2226" s="7">
         <v>3</v>
       </c>
       <c r="H2226" s="12" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="I2226" s="12" t="s">
         <v>1754</v>
@@ -70103,7 +70104,7 @@
     </row>
     <row r="2227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2227" s="9" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B2227" s="5" t="s">
         <v>2768</v>
@@ -70114,13 +70115,13 @@
       </c>
       <c r="E2227" s="11"/>
       <c r="F2227" s="7" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="G2227" s="7">
         <v>3</v>
       </c>
       <c r="H2227" s="12" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="I2227" s="12" t="s">
         <v>1756</v>
@@ -70128,7 +70129,7 @@
     </row>
     <row r="2228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2228" s="9" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B2228" s="5" t="s">
         <v>2768</v>
@@ -70139,13 +70140,13 @@
       </c>
       <c r="E2228" s="11"/>
       <c r="F2228" s="7" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="G2228" s="7">
         <v>3</v>
       </c>
       <c r="H2228" s="12" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="I2228" s="12" t="s">
         <v>1746</v>
@@ -70153,7 +70154,7 @@
     </row>
     <row r="2229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2229" s="9" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B2229" s="5" t="s">
         <v>2768</v>
@@ -70164,13 +70165,13 @@
       </c>
       <c r="E2229" s="11"/>
       <c r="F2229" s="7" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="G2229" s="7">
         <v>3</v>
       </c>
       <c r="H2229" s="12" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="I2229" s="12" t="s">
         <v>1761</v>
@@ -70178,7 +70179,7 @@
     </row>
     <row r="2230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2230" s="9" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B2230" s="5" t="s">
         <v>2768</v>
@@ -70189,13 +70190,13 @@
       </c>
       <c r="E2230" s="11"/>
       <c r="F2230" s="7" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="G2230" s="7">
         <v>3</v>
       </c>
       <c r="H2230" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2230" s="12" t="s">
         <v>1758</v>
@@ -70203,7 +70204,7 @@
     </row>
     <row r="2231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2231" s="9" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="B2231" s="5" t="s">
         <v>2768</v>
@@ -70214,13 +70215,13 @@
       </c>
       <c r="E2231" s="11"/>
       <c r="F2231" s="7" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="G2231" s="7">
         <v>3</v>
       </c>
       <c r="H2231" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2231" s="12" t="s">
         <v>2412</v>
@@ -70228,7 +70229,7 @@
     </row>
     <row r="2232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2232" s="9" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="B2232" s="5" t="s">
         <v>2768</v>
@@ -70239,13 +70240,13 @@
       </c>
       <c r="E2232" s="11"/>
       <c r="F2232" s="7" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="G2232" s="7">
         <v>3</v>
       </c>
       <c r="H2232" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2232" s="12" t="s">
         <v>2413</v>
@@ -70253,7 +70254,7 @@
     </row>
     <row r="2233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2233" s="9" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="B2233" s="5" t="s">
         <v>2768</v>
@@ -70264,13 +70265,13 @@
       </c>
       <c r="E2233" s="11"/>
       <c r="F2233" s="7" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="G2233" s="7">
         <v>3</v>
       </c>
       <c r="H2233" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2233" s="12" t="s">
         <v>2422</v>
